--- a/tame_output/ON/bt/strategyON_20240825.xlsx
+++ b/tame_output/ON/bt/strategyON_20240825.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.3%</t>
+          <t>-665.2%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.4%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -49069,10 +49069,10 @@
         <v>4.194069601255854</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.037489381455164</v>
+        <v>-5.036102023452376</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.178717424360041</v>
+        <v>2.179272367561156</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6828838629545593</v>

--- a/tame_output/ON/bt/strategyON_20240825.xlsx
+++ b/tame_output/ON/bt/strategyON_20240825.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-57.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.1%</t>
+          <t>429.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.2%</t>
+          <t>-682.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-165.4%</t>
         </is>
       </c>
     </row>
@@ -49069,10 +49069,10 @@
         <v>4.194069601255854</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.036102023452376</v>
+        <v>-5.213125921911278</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.179272367561156</v>
+        <v>2.108462808177595</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6828838629545593</v>

--- a/tame_output/ON/bt/strategyON_20240825.xlsx
+++ b/tame_output/ON/bt/strategyON_20240825.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>92.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2066"/>
+  <dimension ref="A1:G2067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.636558194858761</v>
+        <v>3.794507029299167</v>
       </c>
       <c r="C2066" t="n">
         <v>4.194069601255854</v>
@@ -49079,6 +49079,29 @@
       </c>
       <c r="G2066" t="n">
         <v>4.60379991902859</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="2" t="n">
+        <v>45529</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>3.637221052057935</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>4.037604215576652</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>-5.213125921911278</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>2.108462808177595</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>0.6828838629545593</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>4.030668012563019</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240825.xlsx
+++ b/tame_output/ON/bt/strategyON_20240825.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>107.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-55.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>429.7%</t>
+          <t>430.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.9%</t>
+          <t>-679.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.4%</t>
+          <t>-164.1%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.7%</t>
+          <t>-330.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-08-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2067"/>
+  <dimension ref="A1:G2066"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.800598677444288</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.497590663137656</v>
+        <v>-4.466907857236867</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.066788075130935</v>
+        <v>2.07906119749125</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9892887319584955</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.68855090649102</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.515663171429267</v>
+        <v>-4.484980365528479</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.05955907181429</v>
+        <v>2.071832194174606</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9892887319584955</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.691852407792149</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.746836965305899</v>
+        <v>-4.716154159405111</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.927341467857104</v>
+        <v>1.93961459021742</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9892887319584955</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.7673768536529</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.715550944765444</v>
+        <v>-4.684868138864656</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.946878495070226</v>
+        <v>1.959151617430542</v>
       </c>
       <c r="F2050" t="n">
         <v>1.020574752498951</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.752374178387138</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.56252555265216</v>
+        <v>-4.531842746751371</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.107259651488444</v>
+        <v>2.119532773848759</v>
       </c>
       <c r="F2051" t="n">
         <v>1.173600144612235</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.763082037783198</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.59083286652543</v>
+        <v>-4.560150060624641</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.283402950847428</v>
+        <v>2.295676073207744</v>
       </c>
       <c r="F2052" t="n">
         <v>1.173600144612235</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.720919320612483</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.757426091638952</v>
+        <v>-4.726743285738164</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.186168612156102</v>
+        <v>2.198441734516417</v>
       </c>
       <c r="F2053" t="n">
         <v>1.007006919498713</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.729986224277697</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.584361712256652</v>
+        <v>-4.553678906355864</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.25907076657074</v>
+        <v>2.271343888931055</v>
       </c>
       <c r="F2054" t="n">
         <v>1.007006919498713</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.762385106391519</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.555115731800956</v>
+        <v>-4.524432925900167</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.268387213876514</v>
+        <v>2.280660336236829</v>
       </c>
       <c r="F2055" t="n">
         <v>1.007006919498713</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.721208347248422</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.662041279678807</v>
+        <v>-4.631358473778018</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.222910233883008</v>
+        <v>2.235183356243323</v>
       </c>
       <c r="F2056" t="n">
         <v>0.9000813716208612</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.711746305693052</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.807059838186055</v>
+        <v>-4.776377032285267</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.166331612623343</v>
+        <v>2.178604734983658</v>
       </c>
       <c r="F2057" t="n">
         <v>0.7550628131136127</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.733656134679063</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.925401603970773</v>
+        <v>-4.894718798069984</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.218926145567209</v>
+        <v>2.231199267927524</v>
       </c>
       <c r="F2058" t="n">
         <v>0.7657488516765028</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.736682756782853</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.976812026291481</v>
+        <v>-4.946129220390692</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.196147673764864</v>
+        <v>2.208420796125179</v>
       </c>
       <c r="F2059" t="n">
         <v>0.7657488516765028</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.72656165442938</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.056231477499233</v>
+        <v>-5.025548671598444</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.164283021356053</v>
+        <v>2.176556143716368</v>
       </c>
       <c r="F2060" t="n">
         <v>0.7657488516765028</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.758608657290448</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.15169447541645</v>
+        <v>-5.121011669515662</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.126091715747209</v>
+        <v>2.138364838107525</v>
       </c>
       <c r="F2061" t="n">
         <v>0.7657488516765028</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.73717666521005</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.191714473460234</v>
+        <v>-5.161031667559445</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.108180113092307</v>
+        <v>2.120453235452622</v>
       </c>
       <c r="F2062" t="n">
         <v>0.7257288536327189</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.757893118345585</v>
       </c>
       <c r="C2063" t="n">
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.247083635592428</v>
+        <v>-5.216400829691639</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.091766265987156</v>
+        <v>2.104039388347471</v>
       </c>
       <c r="F2063" t="n">
         <v>0.7257288536327189</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.758626575105328</v>
       </c>
       <c r="C2064" t="n">
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.292521415423255</v>
+        <v>-5.261838609522466</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.073129517397758</v>
+        <v>2.085402639758073</v>
       </c>
       <c r="F2064" t="n">
         <v>0.6828838629545593</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.812076205105737</v>
       </c>
       <c r="C2065" t="n">
         <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.20929595857559</v>
+        <v>-5.178613152674802</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.126294092987143</v>
+        <v>2.138567215347458</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6828838629545593</v>
@@ -49063,45 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299167</v>
+        <v>3.816227727852949</v>
       </c>
       <c r="C2066" t="n">
         <v>4.194069601255854</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.213125921911278</v>
+        <v>-5.182443116010489</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.108462808177595</v>
+        <v>2.120735930537911</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6828838629545593</v>
       </c>
       <c r="G2066" t="n">
         <v>4.60379991902859</v>
-      </c>
-    </row>
-    <row r="2067">
-      <c r="A2067" s="2" t="n">
-        <v>45529</v>
-      </c>
-      <c r="B2067" t="n">
-        <v>3.637221052057935</v>
-      </c>
-      <c r="C2067" t="n">
-        <v>4.037604215576652</v>
-      </c>
-      <c r="D2067" t="n">
-        <v>-5.213125921911278</v>
-      </c>
-      <c r="E2067" t="n">
-        <v>2.108462808177595</v>
-      </c>
-      <c r="F2067" t="n">
-        <v>0.6828838629545593</v>
-      </c>
-      <c r="G2067" t="n">
-        <v>4.030668012563019</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240825.xlsx
+++ b/tame_output/ON/bt/strategyON_20240825.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>110.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-36.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.9%</t>
+          <t>429.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.8%</t>
+          <t>-663.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.1%</t>
+          <t>-154.4%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.8%</t>
+          <t>-330.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-157.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2066"/>
+  <dimension ref="A1:G2067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785784</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.038813528646511</v>
       </c>
       <c r="D1904" t="n">
         <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.2840373284408528</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.776814818600139</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.034181015393538</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.3323150046402348</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.851547589525698</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.036996076081175</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.3974253983517682</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>2.94780564974918</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.049902417304833</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.444317606267155</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.01169079101043</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.69293185560764</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.921926487705615</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.2741056807586943</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.820360867547349</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987897</v>
+        <v>3.770422583987896</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.970470829582701</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.3499438564859516</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>2.879954403147956</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.850591906894533</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.2892409503608238</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.772268030004923</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.7235662294092</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.841877920641055</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.3017147730089409</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.795335757103839</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098105</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.834917308545962</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.3610694392979643</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.788375145008746</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493416</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.849379662927105</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.3888770762706146</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.802837499389889</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.8439117833863</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.4267128515788183</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.797369619849084</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792041</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.841409877396877</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.4735273995162479</v>
       </c>
       <c r="F1915" t="n">
         <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.868842394749939</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919903</v>
+        <v>3.812453678919901</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.849110855634202</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.5023071246060895</v>
       </c>
       <c r="F1916" t="n">
         <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>2.908161493266039</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.844891563981253</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.595594009746518</v>
       </c>
       <c r="F1917" t="n">
         <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>2.90394220161309</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.82431123305752</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.847015877901269</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.6336285926171228</v>
       </c>
       <c r="F1918" t="n">
         <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>2.943026182481692</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.839757952884971</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.7263108251804549</v>
       </c>
       <c r="F1919" t="n">
         <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>2.935768257465394</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011491</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.84335707640562</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.8002667856880765</v>
       </c>
       <c r="F1920" t="n">
         <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>2.939367380986043</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392979</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.856684582460173</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>0.8821728769516155</v>
       </c>
       <c r="F1921" t="n">
         <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.055562764854074</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632774</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.85570506007647</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.030247754613955</v>
+        <v>0.9132022694115607</v>
       </c>
       <c r="F1922" t="n">
         <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.102596614735844</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.860399861130788</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.060396852561846</v>
+        <v>0.9433513673594518</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.145472861130521</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.841594119914583</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.698032855427576</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.079070038632199</v>
+        <v>0.9620245534298055</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.126667119914317</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242287</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.843337196539461</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.708535478492865</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.076612066030961</v>
+        <v>0.9595665808285674</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.122108622700021</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.821593509367677</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.847266510374281</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.109438407134259</v>
+        <v>0.9923929219318655</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.126037936534841</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879958</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.847945094291621</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.618579223443805</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117202465802746</v>
+        <v>1.000156980600352</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.128625317790331</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.84861662650233</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.844943165511614</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.509774337964078</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.15772249121463</v>
+        <v>1.040677006012236</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.125623389010325</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.846522202522229</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.289753539927068</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247309847440048</v>
+        <v>1.130264362237654</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.211934333061727</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.862416385324052</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.199305620664789</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.227828515863551</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.863562229764354</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.24852069845089</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.301078210322552</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.873650332325794</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.312710145544321</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.392318329681978</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.859687823727219</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.27479770600267</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.342430924668788</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.874976992961428</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.338014967601213</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.357720093902997</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.78262119228387</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.244671284338932</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.263882469348355</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003595</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.701883053769171</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.13658507129463</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.188709750255385</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508364</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.692319762401062</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.121506558787702</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.179146458887276</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>2.829350599093265</v>
       </c>
       <c r="D1938" t="n">
         <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.236329365122869</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.316177295579479</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>2.833917831085052</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.311086301031644</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.320744527571267</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225437</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>2.809659859846259</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.798263389764238</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.407043564829211</v>
+        <v>1.289998079626817</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.296486556332474</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>2.738198173247709</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.791985187194389</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.3380931592586</v>
+        <v>1.221047674056206</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8176560300468725</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.345837276478227</v>
+        <v>3.228791791275833</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>2.748370559679842</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.732132567990666</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.372206593372222</v>
+        <v>1.255161108169828</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8176560300468725</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.356009662910359</v>
+        <v>3.238964177707965</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>2.743316830253702</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.645889104964288</v>
+        <v>-3.773669513255804</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.401650249156633</v>
+        <v>1.233492600637633</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8176560300468725</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.35095593348422</v>
+        <v>3.233910448281826</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>2.735092605698227</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.691195924363268</v>
+        <v>-3.818976332654784</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.375303296841567</v>
+        <v>1.207145648322567</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7768458670376417</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.318245611123206</v>
+        <v>3.201200125920812</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>2.735644478731329</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.72022902906557</v>
+        <v>-3.848009437357085</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.364241927993748</v>
+        <v>1.196084279474747</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7768458670376417</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.318797484156308</v>
+        <v>3.201751998953914</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>2.664917170622695</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.62741854761471</v>
+        <v>-3.755198955906226</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.330638812465457</v>
+        <v>1.162481163946457</v>
       </c>
       <c r="F1946" t="n">
         <v>0.869656348488501</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.303756464918189</v>
+        <v>3.186710979715795</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>2.666790646547295</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.671808016944138</v>
+        <v>-3.799588425235654</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.314756500658287</v>
+        <v>1.146598852139287</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8252668791590734</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.278996259245134</v>
+        <v>3.16195077404274</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>2.661866355059018</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.788349622049481</v>
+        <v>-3.916130030340997</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.263215567127873</v>
+        <v>1.095057918608872</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7087252740537306</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.204147004693651</v>
+        <v>3.087101519491257</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>2.667357650889686</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.828273716632053</v>
+        <v>-3.956054124923568</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.252737225125511</v>
+        <v>1.084579576606511</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7087252740537306</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.209638300524318</v>
+        <v>3.092592815321924</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>2.678854852658225</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.856054114533406</v>
+        <v>-3.983834522824921</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.253122267733509</v>
+        <v>1.084964619214509</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6809448761523775</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.204467263552045</v>
+        <v>3.087421778349651</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>2.517210572658878</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.974434787263544</v>
+        <v>-4.102215195555059</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.044125718642107</v>
+        <v>0.875968070123107</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6137270240014013</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.002492272262113</v>
+        <v>2.885446787059719</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>2.637360233378084</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.083048865706875</v>
+        <v>-4.210829273998391</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.12082974798398</v>
+        <v>0.9526720994649802</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6137270240014013</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.122641932981319</v>
+        <v>3.005596447778925</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>2.651873259480407</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.047639827458732</v>
+        <v>-4.175420235750248</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14950638938556</v>
+        <v>0.9813487408665602</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6137270240014013</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.137154959083642</v>
+        <v>3.020109473881248</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>2.649292700822775</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.009256164900581</v>
+        <v>-4.137036573192097</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.16227929575119</v>
+        <v>0.9941216472321894</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6521106865595525</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.157604597960901</v>
+        <v>3.040559112758507</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>2.646021729668077</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.832139834865415</v>
+        <v>-3.95992024315693</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.229854856610558</v>
+        <v>1.061697208091558</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6521106865595525</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.154333626806203</v>
+        <v>3.037288141603809</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>2.64670512142999</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.877232079698961</v>
+        <v>-4.005012487990476</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.212501350439053</v>
+        <v>1.044343701920053</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5902146433901627</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.117879392666482</v>
+        <v>3.000833907464088</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>2.640492096736405</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.697856658460193</v>
+        <v>-3.825637066751709</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.278038494240974</v>
+        <v>1.109880845721974</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7469914015608814</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.205732422875328</v>
+        <v>3.088686937672934</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>2.621299552067994</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.742870871980799</v>
+        <v>-3.870651280272315</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.240840264164321</v>
+        <v>1.072682615645321</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7166425062462768</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.168330541018155</v>
+        <v>3.051285055815761</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>2.62699111440694</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.009875382253234</v>
+        <v>-4.13765579054475</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.139730022394293</v>
+        <v>0.9715723738752928</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5222794682033283</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.057404280531332</v>
+        <v>2.940358795328938</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>2.626195036303442</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.111073163690407</v>
+        <v>-4.238853571981923</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.098454831715925</v>
+        <v>0.9302971831969251</v>
       </c>
       <c r="F1960" t="n">
         <v>0.4538706546580091</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.015562914300641</v>
+        <v>2.898517429098247</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>2.623794997857758</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.104562197076095</v>
+        <v>-4.23234260536761</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098659179915967</v>
+        <v>0.9305015313969669</v>
       </c>
       <c r="F1961" t="n">
         <v>0.4538706546580091</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.013162875854958</v>
+        <v>2.896117390652564</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>2.620319717066003</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.085524069368797</v>
+        <v>-4.213304477660313</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102799150207131</v>
+        <v>0.9346415016881309</v>
       </c>
       <c r="F1962" t="n">
         <v>0.3956870433268145</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.974777428264486</v>
+        <v>2.857731943062092</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.856659603902588</v>
+        <v>2.739614118700194</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.138039871643618</v>
+        <v>-4.265820279935133</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201087230931393</v>
+        <v>1.032929582412393</v>
       </c>
       <c r="F1963" t="n">
         <v>0.3956870433268145</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.094071829898676</v>
+        <v>2.977026344696283</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.857492932888721</v>
+        <v>2.740447447686327</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.151906632977536</v>
+        <v>-4.279687041269051</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.19637385538396</v>
+        <v>1.028216206864959</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3578291265929916</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.072190408844516</v>
+        <v>2.955144923642123</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.863501463285647</v>
+        <v>2.746455978083253</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.107102461437606</v>
+        <v>-4.234882869729121</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.220304054396858</v>
+        <v>1.052146405877857</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3578291265929916</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.078198939241442</v>
+        <v>2.961153454039049</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.761451684562847</v>
+        <v>2.644406199360453</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.959359491202604</v>
+        <v>-4.087139899494119</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.177351463768058</v>
+        <v>1.009193815249058</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5256364838278748</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.076833574859572</v>
+        <v>2.959788089657178</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.647199820891934</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.043180712477302</v>
+        <v>-4.170961120768817</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.14661659678966</v>
+        <v>0.9784589482706594</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5256364838278748</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.079627196391053</v>
+        <v>2.962581711188659</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.647862169283592</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.037028006424517</v>
+        <v>-4.164808414716033</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.149740027602432</v>
+        <v>0.9815823790834315</v>
       </c>
       <c r="F1968" t="n">
         <v>0.531789189880659</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.083981168414382</v>
+        <v>2.966935683211988</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.646942646023702</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.053837304575019</v>
+        <v>-4.181617712866535</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.142096785082341</v>
+        <v>0.973939136563341</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5149798917301573</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.072976066264191</v>
+        <v>2.955930581061797</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.713278199820523</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.991539305798897</v>
+        <v>-4.119319714090413</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.233351538389611</v>
+        <v>1.065193889870611</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5602741560045994</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.166488178625677</v>
+        <v>3.049442693423283</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.51557020153465</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.789749108133739</v>
+        <v>-3.917529516425255</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.116359619169801</v>
+        <v>0.9482019706508011</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7582923481737538</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.087591095641296</v>
+        <v>2.970545610438903</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.585860433856825</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.840635820819934</v>
+        <v>-3.968416229111449</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.166295166417498</v>
+        <v>0.9981375178984984</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7074056354875593</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.127349300351755</v>
+        <v>3.010303815149361</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.600488169972869</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.754025078170127</v>
+        <v>-3.881805486461642</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.215567199593465</v>
+        <v>1.047409551074465</v>
       </c>
       <c r="F1973" t="n">
         <v>0.7860313666927176</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.189152475190894</v>
+        <v>3.0721069899885</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.599024150797541</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.814234376175411</v>
+        <v>-3.942014784466926</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.190019461216023</v>
+        <v>1.021861812697023</v>
       </c>
       <c r="F1974" t="n">
         <v>0.725822068687433</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.151562877212394</v>
+        <v>3.034517392010001</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.597515768837469</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.737812329743484</v>
+        <v>-3.865592738035</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.219079897828722</v>
+        <v>1.050922249309722</v>
       </c>
       <c r="F1975" t="n">
         <v>0.725822068687433</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.150054495252323</v>
+        <v>3.033009010049929</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.597378636272905</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.693439198104916</v>
+        <v>-3.821219606396431</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.236692017919586</v>
+        <v>1.068534369400586</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7701952003260016</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.1765412416709</v>
+        <v>3.059495756468507</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.591772430411496</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.715919548963801</v>
+        <v>-3.843699957255316</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.222093671714622</v>
+        <v>1.053936023195622</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7701952003260016</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.170935035809491</v>
+        <v>3.053889550607097</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.598154187439301</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.668263818402745</v>
+        <v>-3.79604422669426</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.247537720966849</v>
+        <v>1.079380072447849</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8178509308870573</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.205910231173929</v>
+        <v>3.088864745971535</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.603046560814025</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.567745659903991</v>
+        <v>-3.695526068195505</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.292637357741076</v>
+        <v>1.124479709222076</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9183690893858119</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.271113499647907</v>
+        <v>3.154068014445513</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.589801233289898</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.551840330471638</v>
+        <v>-3.679620738763153</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.285754161989889</v>
+        <v>1.117596513470889</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8392564286765729</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.210400575698236</v>
+        <v>3.093355090495842</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.593898935900526</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.50700192886324</v>
+        <v>-3.634782337154755</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.307787225243877</v>
+        <v>1.139629576724877</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8437998616214424</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.217224338075786</v>
+        <v>3.100178852873392</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.598059875531604</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.526500385105248</v>
+        <v>-3.654280793396763</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.304148782378152</v>
+        <v>1.135991133859152</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7957152203415381</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.192534492938921</v>
+        <v>3.075489007736527</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.603939478059441</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.482297548019348</v>
+        <v>-3.610077956310862</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.327709519740349</v>
+        <v>1.159551871221349</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8399180574274385</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.224935797718299</v>
+        <v>3.107890312515905</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.602349478528689</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.489857213856395</v>
+        <v>-3.617637622147909</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.323095653874778</v>
+        <v>1.154938005355778</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8947214614372578</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.256227840593438</v>
+        <v>3.139182355391044</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.653597243711729</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.331565796317122</v>
+        <v>-3.459346204608637</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.437659986073526</v>
+        <v>1.269502337554526</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8947214614372578</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.307475605776477</v>
+        <v>3.190430120574083</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.652037948305982</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.123923792682646</v>
+        <v>-3.251704200974161</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51915749212157</v>
+        <v>1.35099984360257</v>
       </c>
       <c r="F1986" t="n">
         <v>1.102363465071734</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.430501512551416</v>
+        <v>3.313456027349022</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.646986176544252</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.072891699960118</v>
+        <v>-3.200672108251633</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.534518557448851</v>
+        <v>1.366360908929851</v>
       </c>
       <c r="F1987" t="n">
         <v>1.153395557794262</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.456068996423203</v>
+        <v>3.339023511220809</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.664173580636957</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.007667518832912</v>
+        <v>-3.135447927124427</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.577795633992438</v>
+        <v>1.409637985473438</v>
       </c>
       <c r="F1988" t="n">
         <v>1.218619738921468</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.512390909192232</v>
+        <v>3.395345423989838</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.660134552936237</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.970240498761779</v>
+        <v>-3.098020907053293</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.588727414320172</v>
+        <v>1.420569765801172</v>
       </c>
       <c r="F1989" t="n">
         <v>1.223871276950649</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.511502804309021</v>
+        <v>3.394457319106627</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.661391345267477</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.990352154796487</v>
+        <v>-3.118132563088002</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.581939544237529</v>
+        <v>1.413781895718529</v>
       </c>
       <c r="F1990" t="n">
         <v>1.234898621948069</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.519376003638713</v>
+        <v>3.402330518436319</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.821949116288688</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961938891696603</v>
+        <v>-3.089719299988118</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.753862620498693</v>
+        <v>1.585704971979694</v>
       </c>
       <c r="F1991" t="n">
         <v>1.17592305920164</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644548437012066</v>
+        <v>3.527502951809672</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>2.942062025506505</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.887156630671591</v>
+        <v>-3.014937038963105</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.903888434126516</v>
+        <v>1.735730785607516</v>
       </c>
       <c r="F1992" t="n">
         <v>1.250705320226652</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809530702844891</v>
+        <v>3.692485217642497</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.933770001520364</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.861072546407783</v>
+        <v>-2.988852954699297</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.906030043845898</v>
+        <v>1.737872395326898</v>
       </c>
       <c r="F1993" t="n">
         <v>1.250705320226652</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.80123867885875</v>
+        <v>3.684193193656356</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.931963197104144</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.773194633298662</v>
+        <v>-2.900975041590177</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.939374404673326</v>
+        <v>1.771216756154326</v>
       </c>
       <c r="F1994" t="n">
         <v>1.366630962650004</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.86898725989654</v>
+        <v>3.751941774694146</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>2.949517602830935</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.764302171905379</v>
+        <v>-2.892082580196893</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.96048579495743</v>
+        <v>1.79232814643843</v>
       </c>
       <c r="F1995" t="n">
         <v>1.366630962650004</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886541665623331</v>
+        <v>3.769496180420937</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.79442494194536</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>2.941372650235519</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.932778288875256</v>
+        <v>-3.060558697166771</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884950395574063</v>
+        <v>1.716792747055063</v>
       </c>
       <c r="F1996" t="n">
         <v>1.338683126933423</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.861628011597967</v>
+        <v>3.744582526395573</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.922642347423381</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.486522096245817</v>
+        <v>-2.614302504537331</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.044722569813701</v>
+        <v>1.876564921294701</v>
       </c>
       <c r="F1997" t="n">
         <v>1.24396445726379</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.786066506984049</v>
+        <v>3.669021021781655</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.913306369920285</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.463800992562664</v>
+        <v>-2.591581400854179</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.044475033783867</v>
+        <v>1.876317385264867</v>
       </c>
       <c r="F1998" t="n">
         <v>1.24396445726379</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.776730529480953</v>
+        <v>3.65968504427856</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.072212495771454</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.593002805856707</v>
+        <v>-2.720783214148221</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.151700434317418</v>
+        <v>1.983542785798419</v>
       </c>
       <c r="F1999" t="n">
         <v>1.114762643969748</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.858115567355697</v>
+        <v>3.741070082153303</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.109290318265101</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.618877204330732</v>
+        <v>-2.746657612622247</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.178428497421455</v>
+        <v>2.010270848902455</v>
       </c>
       <c r="F2000" t="n">
         <v>1.159674252681489</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.922140355076388</v>
+        <v>3.805094869873995</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.105965674254646</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.611822514115559</v>
+        <v>-2.739602922407073</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177925729497069</v>
+        <v>2.00976808097807</v>
       </c>
       <c r="F2001" t="n">
         <v>1.166728942896663</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.923048525195038</v>
+        <v>3.806003039992644</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.115971827899388</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.584871289789071</v>
+        <v>-2.712651698080585</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.198712372872406</v>
+        <v>2.030554724353406</v>
       </c>
       <c r="F2002" t="n">
         <v>1.181609288924382</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.941982886456411</v>
+        <v>3.824937401254017</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.300074960044348</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.720824297845387</v>
+        <v>-2.848604706136902</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.328434301794839</v>
+        <v>2.160276653275839</v>
       </c>
       <c r="F2003" t="n">
         <v>1.181609288924382</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.126086018601371</v>
+        <v>4.009040533398977</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.292191654947341</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.743232415650259</v>
+        <v>-2.871012823941774</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.311587749575883</v>
+        <v>2.143430101056884</v>
       </c>
       <c r="F2004" t="n">
         <v>1.181609288924382</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.118202713504364</v>
+        <v>4.00115722830197</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.294245654496978</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.771456651227859</v>
+        <v>-2.899237059519374</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.302352054894481</v>
+        <v>2.134194406375481</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.19958604137569</v>
+        <v>1.181609288924382</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.131042764524786</v>
+        <v>4.003211227851607</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.350499372218825</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.780897577116389</v>
+        <v>-2.908677985407904</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.354829402260916</v>
+        <v>2.186671753741916</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.322013158919082</v>
+        <v>1.304036406467773</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.260752752772668</v>
+        <v>4.132921216099489</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.353390466764126</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.960951592743545</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.168653405352961</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.251762799132132</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.104448146243405</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.351502279657901</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-3.037281570344451</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.136233227206374</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.251762799132132</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.102559959137181</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.346322509260764</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.239535290668805</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.050151968679494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.049509078807778</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>3.976027956545431</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.344756519470916</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.40110371619606</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>1.983958608678745</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.922726155009899</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>3.898392212476856</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.357829926336835</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.381623969774664</v>
+        <v>-3.509404378066179</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.121869399315615</v>
+        <v>1.953711750796615</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.922726155009899</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>3.911465619342774</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.349835123119774</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.474771441078031</v>
+        <v>-3.602551849369546</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.076615607577208</v>
+        <v>1.908457959058209</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.817873696178675</v>
+        <v>0.7998969437273662</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.957604826029374</v>
+        <v>3.829773289356194</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.348359164246776</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.502672228187504</v>
+        <v>-3.630452636479019</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.063979333860422</v>
+        <v>1.895821685341422</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7832767720357402</v>
+        <v>0.7653000195844314</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.935370712670615</v>
+        <v>3.807539175997436</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.345123608223975</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.625198330890398</v>
+        <v>-3.752978739181913</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.011733336756463</v>
+        <v>1.843575688237463</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6607506693328463</v>
+        <v>0.6427739168815375</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.858619495026077</v>
+        <v>3.730787958352898</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.411829567814479</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.855712827075987</v>
+        <v>-3.983493235367502</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.986233497872731</v>
+        <v>1.818075849353731</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4302361731472576</v>
+        <v>0.4122594206959488</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.787016756905228</v>
+        <v>3.659185220232049</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.552141286816326</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.11243364507081</v>
+        <v>-4.240214053362326</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.023856889676648</v>
+        <v>1.855699241157648</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3218215990034428</v>
+        <v>0.303844846552134</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.862279731420786</v>
+        <v>3.734448194747606</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.621121555961966</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.266420062846951</v>
+        <v>-4.394200471138467</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.031242591711832</v>
+        <v>1.863084943192832</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3218215990034428</v>
+        <v>0.303844846552134</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.931260000566426</v>
+        <v>3.803428463893246</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423382</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.607172758082087</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.215898159019285</v>
+        <v>-4.343678567310801</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.037502555363019</v>
+        <v>1.869344906844019</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3218215990034428</v>
+        <v>0.303844846552134</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.917311202686546</v>
+        <v>3.789479666013367</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609748</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.619043247137501</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.468373313027009</v>
+        <v>-4.596153721318525</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.948382982815343</v>
+        <v>1.780225334296343</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3218215990034428</v>
+        <v>0.303844846552134</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.92918169174196</v>
+        <v>3.801350155068781</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.620253781656444</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.761269069506421</v>
+        <v>-4.889049477797937</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.832435214742522</v>
+        <v>1.664277566223522</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3218215990034428</v>
+        <v>0.303844846552134</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.930392226260905</v>
+        <v>3.802560689587725</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251941</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.624375523883766</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.94793319764123</v>
+        <v>-5.075713605932745</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.761891305715921</v>
+        <v>1.59373365719692</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2950826281788829</v>
+        <v>0.2771058757275741</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.918470585993489</v>
+        <v>3.790639049320311</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.619453376619955</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.093953884555192</v>
+        <v>-5.221734292846707</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.698560883686525</v>
+        <v>1.530403235167525</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2859995363850259</v>
+        <v>0.2680227839337171</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.908098583653365</v>
+        <v>3.780267046980186</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.781657433318999</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.185667893664776</v>
+        <v>-5.313448301956292</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.824079336741736</v>
+        <v>1.655921688222735</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2859995363850259</v>
+        <v>0.2680227839337171</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.070302640352409</v>
+        <v>3.94247110367923</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.776504071282814</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.217319552724746</v>
+        <v>-5.345099961016262</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.806265311081562</v>
+        <v>1.638107662562561</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2808310791405857</v>
+        <v>0.2628543266892769</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.062048203969559</v>
+        <v>3.93421666729638</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.786733488851305</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.299254370993629</v>
+        <v>-5.427034779285145</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.7837208013425</v>
+        <v>1.615563152823499</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2708963335535055</v>
+        <v>0.2529195811021967</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.066316774185802</v>
+        <v>3.938485237512623</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.795659127307207</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.401230493242037</v>
+        <v>-5.529010901533552</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.751855990899039</v>
+        <v>1.583698342380039</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1689202113050979</v>
+        <v>0.1509434588537891</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.01405673929266</v>
+        <v>3.886225202619481</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231802</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.787812014551383</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.291224209764815</v>
+        <v>-5.419004618056331</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.788011391534103</v>
+        <v>1.619853743015103</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1921247832223731</v>
+        <v>0.1741480307710643</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.0201323696872</v>
+        <v>3.892300833014021</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.792062025273357</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.148164634023889</v>
+        <v>-5.275945042315405</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.849485232552448</v>
+        <v>1.681327584033448</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2001382098123524</v>
+        <v>0.1821614573610436</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.029190436363162</v>
+        <v>3.901358899689983</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.799322908155893</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.846717908552051</v>
+        <v>-4.974498316843567</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.977324805623719</v>
+        <v>1.809167157104719</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5015849352841897</v>
+        <v>0.4836081828328809</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.217319354528801</v>
+        <v>4.089487817855622</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679619</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.800294085908603</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.871308152787235</v>
+        <v>-4.999088561078751</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.968459885682356</v>
+        <v>1.800302237163356</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5015849352841897</v>
+        <v>0.4836081828328809</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.218290532281511</v>
+        <v>4.090458995608333</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.801136990288359</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.820269776780715</v>
+        <v>-4.948050185072231</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.989718140464719</v>
+        <v>1.821560491945719</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5015849352841897</v>
+        <v>0.4836081828328809</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.219133436661267</v>
+        <v>4.091301899988088</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969537</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.820175089162504</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.779130481914084</v>
+        <v>-4.9069108902056</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.025211957285517</v>
+        <v>1.857054308766517</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5427242301508205</v>
+        <v>0.5247474776995117</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.26285511245539</v>
+        <v>4.135023575782212</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.636359085286439</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.682495569895444</v>
+        <v>-4.81027597818696</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.880049918216907</v>
+        <v>1.711892269697908</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6393591421694604</v>
+        <v>0.6213823897181516</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.137020055790509</v>
+        <v>4.00918851911733</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.639861129360403</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.813076304426287</v>
+        <v>-4.940856712717802</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.831319668478534</v>
+        <v>1.663162019959535</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5087784076386179</v>
+        <v>0.4908016551873091</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.062173659145967</v>
+        <v>3.934342122472788</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.624287948436486</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.648579970235325</v>
+        <v>-4.77636037852684</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.881545021231001</v>
+        <v>1.713387372712002</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6732747418295798</v>
+        <v>0.655297989378271</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.145298278736627</v>
+        <v>4.017466742063449</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077622</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.623475658872915</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.675949902919757</v>
+        <v>-4.803730311211273</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.869784758593658</v>
+        <v>1.701627110074659</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6732747418295798</v>
+        <v>0.655297989378271</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.144485989173057</v>
+        <v>4.016654452499878</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.633344437997988</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.686335097809646</v>
+        <v>-4.814115506101162</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.875499459762775</v>
+        <v>1.707341811243776</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6628895469396905</v>
+        <v>0.6449127944883817</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.148123651364195</v>
+        <v>4.020292114691017</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.704181443774413</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.704923256531871</v>
+        <v>-4.832703664823387</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.93890120205031</v>
+        <v>1.770743553531311</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6443013882174651</v>
+        <v>0.6263246357661563</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.207807761907286</v>
+        <v>4.079976225234107</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.701050454592711</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.705221803227907</v>
+        <v>-4.833002211519423</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.935650794190194</v>
+        <v>1.767493145671195</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6440028415214292</v>
+        <v>0.6260260890701204</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.204497644707963</v>
+        <v>4.076666108034784</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.81564321210885</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.705581349532103</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.604398669537479</v>
+        <v>-4.732179077828995</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.980510942605757</v>
+        <v>1.812353294086757</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.656467057005783</v>
+        <v>0.6384903045544742</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.216507068937966</v>
+        <v>4.088675532264787</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121459</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.705710603010646</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.413617308785073</v>
+        <v>-4.541397717076588</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.056952740385263</v>
+        <v>1.888795091866263</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8472484177581904</v>
+        <v>0.8292716653068816</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.331105138867954</v>
+        <v>4.203273602194775</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906073</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.685547448748243</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.395100454743252</v>
+        <v>-4.522880863034768</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.044196327739588</v>
+        <v>1.876038679220588</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8601785471833986</v>
+        <v>0.8422017947320898</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.318700062260675</v>
+        <v>4.190868525587497</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912978</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.720514385360301</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.33976986684149</v>
+        <v>-4.467550275133005</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.101295499512351</v>
+        <v>1.933137850993352</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9155091350851607</v>
+        <v>0.8975323826338519</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.386865351613791</v>
+        <v>4.259033814940612</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539887</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.714200953261739</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.327715739928527</v>
+        <v>-4.455496148220043</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.099803718178974</v>
+        <v>1.931646069659974</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9275632619981236</v>
+        <v>0.9095865095468147</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.387784395663006</v>
+        <v>4.259952858989828</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811002</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.716081583445875</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.368870859496748</v>
+        <v>-4.496651267788264</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.085222300535821</v>
+        <v>1.917064652016822</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8864081424299026</v>
+        <v>0.8684313899785938</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.36497195410621</v>
+        <v>4.237140417433031</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.728932609323757</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.265990269968155</v>
+        <v>-4.393770678259671</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.139225562225141</v>
+        <v>1.971067913706142</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.9713119795071867</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.439551333701248</v>
+        <v>4.311719797028069</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.800598677444288</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.749135279497351</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.466907857236867</v>
+        <v>-4.625371071429171</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.07906119749125</v>
+        <v>1.898630426611936</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.9713119795071867</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.459754003874842</v>
+        <v>4.331922467201664</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.68855090649102</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.749135279497351</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.484980365528479</v>
+        <v>-4.643443579720783</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.071832194174606</v>
+        <v>1.891401423295291</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.9713119795071867</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.459754003874842</v>
+        <v>4.331922467201664</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.691852407792149</v>
+        <v>3.670068888082828</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.709387193090818</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.716154159405111</v>
+        <v>-4.874617373597415</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.93961459021742</v>
+        <v>1.759183819338105</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9892887319584955</v>
+        <v>0.9713119795071867</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.420005917468308</v>
+        <v>4.29217438079513</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.7673768536529</v>
+        <v>3.74559333394358</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.716409812087758</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.684868138864656</v>
+        <v>-4.84333135305696</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.959151617430542</v>
+        <v>1.778720846551227</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.020574752498951</v>
+        <v>1.002598000047642</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.445800148789522</v>
+        <v>4.317968612116344</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.752374178387138</v>
+        <v>3.730590658677818</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.815580811660662</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.531842746751371</v>
+        <v>-4.690305960943675</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.119532773848759</v>
+        <v>1.939102002969445</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.173600144612235</v>
+        <v>1.155623392160926</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.636786383630397</v>
+        <v>4.508954846957218</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.763082037783198</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>4.003047036568955</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.560150060624641</v>
+        <v>-4.718613274816946</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.295676073207744</v>
+        <v>2.115245302328429</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.173600144612235</v>
+        <v>1.155623392160926</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.824252608538689</v>
+        <v>4.696421071865511</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.720919320612483</v>
+        <v>3.699135800903163</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>3.972449987923037</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.726743285738164</v>
+        <v>-4.885206499930468</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.198441734516417</v>
+        <v>2.018010963637102</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.007006919498713</v>
+        <v>0.9890301670474038</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.693699624824657</v>
+        <v>4.565868088151479</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.729986224277697</v>
+        <v>3.708202704568377</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>3.976126390584755</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.553678906355864</v>
+        <v>-4.712142120548168</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.271343888931055</v>
+        <v>2.09091311805174</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.007006919498713</v>
+        <v>0.9890301670474038</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.697376027486375</v>
+        <v>4.569544490813197</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.762385106391519</v>
+        <v>3.740601586682199</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.090789930910643</v>
+        <v>3.97374444570825</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.524432925900167</v>
+        <v>-4.682896140092471</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.280660336236829</v>
+        <v>2.100229565357514</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.007006919498713</v>
+        <v>0.9890301670474038</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.69499408260987</v>
+        <v>4.567162545936692</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.721208347248422</v>
+        <v>3.699424827539102</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.088083170068278</v>
+        <v>3.971037684865885</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.631358473778018</v>
+        <v>-4.789821687970322</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.235183356243323</v>
+        <v>2.054752585364009</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9000813716208612</v>
+        <v>0.8821046191695524</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.628131993040795</v>
+        <v>4.500300456367617</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.711746305693052</v>
+        <v>3.689962785983732</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.089511972211512</v>
+        <v>3.972466487009119</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.776377032285267</v>
+        <v>-4.934840246477571</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.178604734983658</v>
+        <v>1.998173964104343</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7550628131136127</v>
+        <v>0.7370860606623039</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.54254966007968</v>
+        <v>4.414718123406502</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.733656134679063</v>
+        <v>3.711872614969743</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.189443211469265</v>
+        <v>4.072397726266872</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.894718798069984</v>
+        <v>-5.053182012262289</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.231199267927524</v>
+        <v>2.050768497048209</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.7477720992251939</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.648892522475167</v>
+        <v>4.521060985801989</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.736682756782853</v>
+        <v>3.714899237073533</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.187228908595204</v>
+        <v>4.070183423392811</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.946129220390692</v>
+        <v>-5.104592434582996</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.208420796125179</v>
+        <v>2.027990025245865</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.7477720992251939</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.646678219601106</v>
+        <v>4.518846682927927</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.72656165442938</v>
+        <v>3.70477813472006</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.187132036669493</v>
+        <v>4.0700865514671</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.025548671598444</v>
+        <v>-5.184011885790748</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.176556143716368</v>
+        <v>1.996125372837054</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.7477720992251939</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.646581347675395</v>
+        <v>4.518749811002217</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.758608657290448</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.187125930227537</v>
+        <v>4.070080445025144</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.121011669515662</v>
+        <v>-5.279474883707966</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.138364838107525</v>
+        <v>1.95793406722821</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7657488516765028</v>
+        <v>0.7477720992251939</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.646575241233439</v>
+        <v>4.518743704560261</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.73717666521005</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.185222326790147</v>
+        <v>4.068176841587754</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.161031667559445</v>
+        <v>-5.31949488175175</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.120453235452622</v>
+        <v>1.940022464573307</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7257288536327189</v>
+        <v>0.7077521011814101</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.620659638969779</v>
+        <v>4.492828102296601</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.757893118345585</v>
+        <v>3.736109598636265</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.190956144537874</v>
+        <v>4.073910659335481</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.216400829691639</v>
+        <v>-5.374864043883943</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.104039388347471</v>
+        <v>1.923608617468156</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7257288536327189</v>
+        <v>0.7077521011814101</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.626393456717506</v>
+        <v>4.498561920044327</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.758626575105328</v>
+        <v>3.736843055396008</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.190494507880807</v>
+        <v>4.073449022678414</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.261838609522466</v>
+        <v>-5.42030182371477</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.085402639758073</v>
+        <v>1.904971868878758</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6828838629545593</v>
+        <v>0.6649071105032505</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.600224825653543</v>
+        <v>4.472393288980364</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.812076205105737</v>
+        <v>3.790292685396417</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.210368900731126</v>
+        <v>4.093323415528733</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.178613152674802</v>
+        <v>-5.337076366867106</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.138567215347458</v>
+        <v>1.958136444468143</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6828838629545593</v>
+        <v>0.6649071105032505</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.620099218503862</v>
+        <v>4.492267681830683</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,45 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.816227727852949</v>
+        <v>3.742792842057662</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.194069601255854</v>
+        <v>4.077024116053461</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.182443116010489</v>
+        <v>-5.160786142261799</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.120735930537911</v>
+        <v>2.012353234834994</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6828838629545593</v>
+        <v>0.6649071105032505</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.60379991902859</v>
+        <v>4.475968382355411</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="2" t="n">
+        <v>45529</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>3.592178508075042</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>4.225596458839967</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>-5.018408802494468</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>2.217876513528433</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>0.6649071105032505</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>4.624540725141918</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240825.xlsx
+++ b/tame_output/ON/bt/strategyON_20240825.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>49.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>106.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>110.9%</t>
+          <t>147.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-46.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>429.6%</t>
+          <t>430.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-663.4%</t>
+          <t>-677.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-123.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.4%</t>
+          <t>-319.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-151.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>105.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911635</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213491</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416041</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382323</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495494</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347049</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130011</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178237</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207807</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310976</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.311086391309418</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970899</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191731</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097814</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094109</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.405960511199278</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969586</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923078</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297741</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.424592053374983</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.2298731534084935</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.12998586193028</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.46232857509708</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.458244891883457</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.2388517343274468</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.230399229847317</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.406563108831293</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.384775060216008</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1940921001670461</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.169840522104282</v>
+        <v>-1.156929398179869</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.458270034970535</v>
+        <v>2.466016709325183</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.559899477602551</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.249586646374147</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.332053815566412</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.367750605286126</v>
+        <v>2.375497279640774</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.794351571617041</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.3505866488815386</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.344964939490826</v>
+        <v>-1.332053815566412</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.36053144038453</v>
+        <v>2.368278114739178</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.898726302643487</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.3990087320660933</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.449339670517272</v>
+        <v>-1.436428546592858</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.291234410994686</v>
+        <v>2.298981085349334</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-9.061239768342071</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.462898328506971</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.546973100935959</v>
+        <v>-1.534061977011545</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.23377014258203</v>
+        <v>2.241516816936679</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.187276561710361</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.5106193172251721</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.508810354201803</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.25161484489699</v>
+        <v>2.259361519251638</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-9.13020478981443</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4838002727803987</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.508810354201803</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.255605180583391</v>
+        <v>2.26335185493804</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.27187663153855</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.5419442363687885</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.521721478126216</v>
+        <v>-1.508810354201803</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.254129953684649</v>
+        <v>2.261876628039298</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.222285787113716</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.5070544884339827</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.472130633701382</v>
+        <v>-1.459219509776969</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.298937870504422</v>
+        <v>2.30668454485907</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-9.073367452641859</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4605382882919229</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.440881042966209</v>
+        <v>-1.427969919041796</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.304636491298843</v>
+        <v>2.312383165653491</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.847522299922449</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.36062115416795</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.386043243454632</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.33937156968735</v>
+        <v>2.347118244041998</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.722943643584857</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.3096505470768545</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.398954367379046</v>
+        <v>-1.386043243454632</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.340510714243409</v>
+        <v>2.348257388598057</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.775838931629144</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.3281748881324615</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.381087897366186</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.346117696058584</v>
+        <v>2.353864370413232</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.703705756341263</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2935879137786728</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.393999021290599</v>
+        <v>-1.381087897366186</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351851400297221</v>
+        <v>2.359598074651869</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.632339363731615</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.274778619128679</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.309721504756538</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.384933973469144</v>
+        <v>2.392680647823792</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.538880329746391</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.2472784868474966</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.309721504756538</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.375050492156237</v>
+        <v>2.382797166510885</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.528227148192959</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.2448517747254977</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.322632628680952</v>
+        <v>-1.309721504756538</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.373215931656863</v>
+        <v>2.380962606011511</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.430320109516469</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.2059892742283624</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.254646878820395</v>
+        <v>-1.241735754895982</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.413707066599736</v>
+        <v>2.421453740954384</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.406366568540511</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1957393516924855</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.230693337844438</v>
+        <v>-1.217782213920024</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.428747697330804</v>
+        <v>2.436494371685452</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017766</v>
+        <v>3.789311112017765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.142306630217714</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.1033756925251188</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9537222755972277</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.581670018517378</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.435227006712876</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.1766691232165156</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-0.9537222755972277</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.578882984857077</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.395042708346685</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.1930864664508332</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-0.9135379772310369</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.603337187764633</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.231642837407323</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.2578132360473351</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.7501381062916744</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.700743931549007</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.998161615177724</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.3591301537770266</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.5166568840620759</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.848757093724619</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785784</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.038813528646511</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.848495224170209</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2840373284408528</v>
+        <v>0.4161044998670738</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.4237533928195399</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.776814818600139</v>
+        <v>2.901606978157181</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.034181015393538</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.716219750539323</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3323150046402348</v>
+        <v>0.4643821760664553</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.2914779191886533</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.851547589525698</v>
+        <v>2.97633974908274</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.036996076081175</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.560481417979581</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3974253983517682</v>
+        <v>0.5294925697779886</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.1357395866289117</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.94780564974918</v>
+        <v>3.072597809306222</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.049902417304833</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.475516751250261</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.444317606267155</v>
+        <v>0.5763847776933755</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.05077491989959215</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.01169079101043</v>
+        <v>3.136482950567472</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560764</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.921926487705615</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.581106741023365</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2741056807586943</v>
+        <v>0.4061728521849148</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.1563649096726965</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.820360867547349</v>
+        <v>2.945153027104391</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987896</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.970470829582701</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.512872156397938</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3499438564859516</v>
+        <v>0.4820110279121721</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.1379495868001605</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.879954403147956</v>
+        <v>3.004746562704999</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.850591906894533</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.364932114990339</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2892409503608238</v>
+        <v>0.4213081217870442</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.1176286708916029</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.772268030004923</v>
+        <v>2.897060189561966</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235662294092</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.841877920641055</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.368868712068018</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3017147730089409</v>
+        <v>0.4110194967024947</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1215652679692822</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.795335757103839</v>
+        <v>2.88598424506188</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098105</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.834917308545962</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.203080516107727</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3610694392979643</v>
+        <v>0.4703741629915177</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1215652679692822</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.788375145008746</v>
+        <v>2.879023632966787</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493416</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.849379662927105</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-6.169717309628958</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3888770762706146</v>
+        <v>0.4981817999641684</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1215652679692822</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.802837499389889</v>
+        <v>2.89348598734793</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722812</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.8439117833863</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-6.061458172506437</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4267128515788183</v>
+        <v>0.5360175752723721</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.1215652679692822</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.797369619849084</v>
+        <v>2.888018107807125</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792041</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.841409877396877</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.938167037689306</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4735273995162479</v>
+        <v>0.5828321232098013</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>0.001725866847848256</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.868842394749939</v>
+        <v>2.95949088270798</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919901</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.849110855634202</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.885470170558015</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5023071246060895</v>
+        <v>0.6116118482996429</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.05442273397913944</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.908161493266039</v>
+        <v>2.99880998122408</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318088</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.844891563981253</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.64170472857457</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.595594009746518</v>
+        <v>0.7048987334400714</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>0.05442273397913944</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.90394220161309</v>
+        <v>2.994590689571131</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305752</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.847015877901269</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.551929056198098</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6336285926171228</v>
+        <v>0.7429333163106762</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1160221788934495</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.943026182481692</v>
+        <v>3.033674670439733</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279178</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.839757952884971</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.302078662249023</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7263108251804549</v>
+        <v>0.8356155488740082</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1160221788934495</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.935768257465394</v>
+        <v>3.026416745423435</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011491</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.84335707640562</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-5.126186569781591</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8002667856880765</v>
+        <v>0.9095715093816299</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.1160221788934495</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.939367380986043</v>
+        <v>3.030015868944083</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392979</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.856684582460173</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.954740106759128</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8821728769516155</v>
+        <v>0.9914776006451689</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.2874686419159126</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.055562764854074</v>
+        <v>3.146211252812115</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632774</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.85570506007647</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.855365915877906</v>
+        <v>-4.874717819650007</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9132022694115607</v>
+        <v>1.022506993105114</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.3674909290250336</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.102596614735844</v>
+        <v>3.193245102693885</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883067</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.860399861130788</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.791730173643971</v>
+        <v>-4.811082077416073</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9433513673594518</v>
+        <v>1.052656091053005</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.4311266712589681</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.145472861130521</v>
+        <v>3.236121349088563</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074776</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.841594119914583</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.698032855427576</v>
+        <v>-4.717384759199677</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9620245534298055</v>
+        <v>1.071329277123359</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.4311266712589681</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.126667119914317</v>
+        <v>3.217315607872358</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242287</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.843337196539461</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.708535478492865</v>
+        <v>-4.727887382264966</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9595665808285674</v>
+        <v>1.068871304522121</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4206240481936792</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.122108622700021</v>
+        <v>3.212757110658062</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367677</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.847266510374281</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.636292910321671</v>
+        <v>-4.655644814093772</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9923929219318655</v>
+        <v>1.101697645625419</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.4206240481936792</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.126037936534841</v>
+        <v>3.216686424492883</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879958</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.847945094291621</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.618579223443805</v>
+        <v>-4.637931127215906</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.000156980600352</v>
+        <v>1.109461704293905</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.423805377090596</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.128625317790331</v>
+        <v>3.219273805748373</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650233</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.844943165511614</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.509774337964078</v>
+        <v>-4.529126241736179</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.040677006012236</v>
+        <v>1.149981729705789</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.423805377090596</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.125623389010325</v>
+        <v>3.216271876968366</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675932</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.846522202522229</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.289753539927068</v>
+        <v>-4.309105443699169</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.130264362237654</v>
+        <v>1.239569085931208</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.5650252221585763</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.211934333061727</v>
+        <v>3.302582821019768</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539943</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.862416385324052</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.176237754635891</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.199305620664789</v>
+        <v>1.308610344358342</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.5650252221585763</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.227828515863551</v>
+        <v>3.318477003821592</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.863562229764354</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.056064671271392</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.24852069845089</v>
+        <v>1.357825422144443</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.6851983055230753</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.301078210322552</v>
+        <v>3.391726698280593</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.873650332325794</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.920811309941415</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.312710145544321</v>
+        <v>1.422014869237874</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.8204516668530524</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.392318329681978</v>
+        <v>3.482966817640019</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.859687823727219</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.980686137299108</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.27479770600267</v>
+        <v>1.384102429696223</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7605768394953603</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.342430924668788</v>
+        <v>3.43307941262683</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674509</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.874976992961428</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.86086590638827</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.338014967601213</v>
+        <v>1.447319691294767</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.7605768394953603</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.357720093902997</v>
+        <v>3.448368581861038</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430688</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.78262119228387</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.863335612850076</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.244671284338932</v>
+        <v>1.353976008032486</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.758107133033554</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.263882469348355</v>
+        <v>3.354530957306396</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003595</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.701883053769171</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.931705799174086</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.13658507129463</v>
+        <v>1.245889794988183</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.767382832069769</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.188709750255385</v>
+        <v>3.279358238213427</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508364</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.692319762401062</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.945493852021133</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.121506558787702</v>
+        <v>1.230811282481256</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.767382832069769</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.179146458887276</v>
+        <v>3.269794946845318</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.829350599093265</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-4.001013927913722</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.236329365122869</v>
+        <v>1.345634088816422</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.767382832069769</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.316177295579479</v>
+        <v>3.40682578353752</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.833917831085052</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.825539668121253</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.311086301031644</v>
+        <v>1.420391024725198</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.767382832069769</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.320744527571267</v>
+        <v>3.411393015529308</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225437</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.809659859846259</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.798263389764238</v>
+        <v>-3.817615293536339</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.289998079626817</v>
+        <v>1.39930280332037</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.767382832069769</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.296486556332474</v>
+        <v>3.387135044290515</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.738198173247709</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.791985187194389</v>
+        <v>-3.81133709096649</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.221047674056206</v>
+        <v>1.33035239774976</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8176560300468725</v>
+        <v>0.773661034639618</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.228791791275833</v>
+        <v>3.319440279233874</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.748370559679842</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.732132567990666</v>
+        <v>-3.832909439721919</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.255161108169828</v>
+        <v>1.331895844679721</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8176560300468725</v>
+        <v>0.773661034639618</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.238964177707965</v>
+        <v>3.329612665666006</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.743316830253702</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.773669513255804</v>
+        <v>-3.746665976695541</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.233492600637633</v>
+        <v>1.361339500464132</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8176560300468725</v>
+        <v>0.773661034639618</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.233910448281826</v>
+        <v>3.324558936239867</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.735092605698227</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.818976332654784</v>
+        <v>-3.791972796094521</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.207145648322567</v>
+        <v>1.334992548149065</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7768458670376417</v>
+        <v>0.7328508716303872</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.201200125920812</v>
+        <v>3.291848613878854</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.735644478731329</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.848009437357085</v>
+        <v>-3.821005900796823</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.196084279474747</v>
+        <v>1.323931179301246</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7768458670376417</v>
+        <v>0.7328508716303872</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.201751998953914</v>
+        <v>3.292400486911955</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.664917170622695</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.755198955906226</v>
+        <v>-3.728195419345964</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.162481163946457</v>
+        <v>1.290328063772956</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.869656348488501</v>
+        <v>0.8256613530812466</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.186710979715795</v>
+        <v>3.277359467673837</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.666790646547295</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.799588425235654</v>
+        <v>-3.772584888675391</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.146598852139287</v>
+        <v>1.274445751965786</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8252668791590734</v>
+        <v>0.7812718837518189</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.16195077404274</v>
+        <v>3.252599262000781</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.661866355059018</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.916130030340997</v>
+        <v>-3.889126493780734</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.095057918608872</v>
+        <v>1.222904818435371</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7087252740537306</v>
+        <v>0.6647302786464762</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.087101519491257</v>
+        <v>3.177750007449298</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.667357650889686</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.956054124923568</v>
+        <v>-3.929050588363306</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.084579576606511</v>
+        <v>1.21242647643301</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7087252740537306</v>
+        <v>0.6647302786464762</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.092592815321924</v>
+        <v>3.183241303279965</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.678854852658225</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.983834522824921</v>
+        <v>-3.956830986264659</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.084964619214509</v>
+        <v>1.212811519041008</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6809448761523775</v>
+        <v>0.636949880745123</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.087421778349651</v>
+        <v>3.178070266307693</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.517210572658878</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.102215195555059</v>
+        <v>-4.075211658994797</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.875968070123107</v>
+        <v>1.003814969949606</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6137270240014013</v>
+        <v>0.5697320285941468</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.885446787059719</v>
+        <v>2.97609527501776</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.637360233378084</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.210829273998391</v>
+        <v>-4.183825737438128</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9526720994649802</v>
+        <v>1.080518999291479</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6137270240014013</v>
+        <v>0.5697320285941468</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.005596447778925</v>
+        <v>3.096244935736966</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.651873259480407</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.175420235750248</v>
+        <v>-4.148416699189985</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9813487408665602</v>
+        <v>1.109195640693059</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6137270240014013</v>
+        <v>0.5697320285941468</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.020109473881248</v>
+        <v>3.110757961839289</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.649292700822775</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.137036573192097</v>
+        <v>-4.110033036631834</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9941216472321894</v>
+        <v>1.121968547058688</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6521106865595525</v>
+        <v>0.608115691152298</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.040559112758507</v>
+        <v>3.131207600716548</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.646021729668077</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.95992024315693</v>
+        <v>-3.932916706596668</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.061697208091558</v>
+        <v>1.189544107918057</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6521106865595525</v>
+        <v>0.608115691152298</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.037288141603809</v>
+        <v>3.12793662956185</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.64670512142999</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.005012487990476</v>
+        <v>-3.978008951430214</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.044343701920053</v>
+        <v>1.172190601746552</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5902146433901627</v>
+        <v>0.5462196479829082</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.000833907464088</v>
+        <v>3.091482395422129</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.640492096736405</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.825637066751709</v>
+        <v>-3.798633530191446</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.109880845721974</v>
+        <v>1.237727745548473</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7469914015608814</v>
+        <v>0.7029964061536269</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.088686937672934</v>
+        <v>3.179335425630975</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.621299552067994</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.870651280272315</v>
+        <v>-3.843647743712052</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.072682615645321</v>
+        <v>1.20052951547182</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7166425062462768</v>
+        <v>0.6726475108390223</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.051285055815761</v>
+        <v>3.141933543773802</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.62699111440694</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.13765579054475</v>
+        <v>-4.110652253984488</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9715723738752928</v>
+        <v>1.099419273701792</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5222794682033283</v>
+        <v>0.4782844727960737</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.940358795328938</v>
+        <v>3.031007283286979</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.626195036303442</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.238853571981923</v>
+        <v>-4.21185003542166</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9302971831969251</v>
+        <v>1.058144083023424</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.4098756592507545</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.898517429098247</v>
+        <v>2.989165917056289</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.623794997857758</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.23234260536761</v>
+        <v>-4.205339068807348</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9305015313969669</v>
+        <v>1.058348431223466</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4538706546580091</v>
+        <v>0.4098756592507545</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.896117390652564</v>
+        <v>2.986765878610605</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.620319717066003</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.213304477660313</v>
+        <v>-4.18630094110005</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9346415016881309</v>
+        <v>1.06248840151463</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.35169204791956</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.857731943062092</v>
+        <v>2.948380431020134</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.739614118700194</v>
+        <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.265820279935133</v>
+        <v>-4.238816743374871</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.032929582412393</v>
+        <v>1.160776482238892</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3956870433268145</v>
+        <v>0.35169204791956</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.977026344696283</v>
+        <v>3.067674832654324</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.740447447686327</v>
+        <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.279687041269051</v>
+        <v>-4.252683504708789</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.028216206864959</v>
+        <v>1.156063106691458</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.3138341311857371</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.955144923642123</v>
+        <v>3.045793411600163</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.746455978083253</v>
+        <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.234882869729121</v>
+        <v>-4.207879333168859</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.052146405877857</v>
+        <v>1.179993305704356</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3578291265929916</v>
+        <v>0.3138341311857371</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.961153454039049</v>
+        <v>3.051801941997089</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.644406199360453</v>
+        <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.087139899494119</v>
+        <v>-4.060136362933856</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.009193815249058</v>
+        <v>1.137040715075557</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.4816414884206202</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.959788089657178</v>
+        <v>3.050436577615219</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.647199820891934</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.170961120768817</v>
+        <v>-4.143957584208555</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9784589482706594</v>
+        <v>1.106305848097158</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5256364838278748</v>
+        <v>0.4816414884206202</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.962581711188659</v>
+        <v>3.0532301991467</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.647862169283592</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.164808414716033</v>
+        <v>-4.13780487815577</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9815823790834315</v>
+        <v>1.10942927890993</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.531789189880659</v>
+        <v>0.4877941944734045</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.966935683211988</v>
+        <v>3.057584171170029</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.646942646023702</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.181617712866535</v>
+        <v>-4.154614176306272</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.973939136563341</v>
+        <v>1.10178603638984</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5149798917301573</v>
+        <v>0.4709848963229029</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.955930581061797</v>
+        <v>3.046579069019838</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.713278199820523</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.119319714090413</v>
+        <v>-4.09231617753015</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.065193889870611</v>
+        <v>1.19304078969711</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5602741560045994</v>
+        <v>0.5162791605973449</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.049442693423283</v>
+        <v>3.140091181381324</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.51557020153465</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.917529516425255</v>
+        <v>-3.890525979864992</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9482019706508011</v>
+        <v>1.0760488704773</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7582923481737538</v>
+        <v>0.7142973527664993</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.970545610438903</v>
+        <v>3.061194098396944</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.585860433856825</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.968416229111449</v>
+        <v>-3.941412692551187</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9981375178984984</v>
+        <v>1.125984417724997</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7074056354875593</v>
+        <v>0.6634106400803048</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.010303815149361</v>
+        <v>3.100952303107403</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.600488169972869</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.881805486461642</v>
+        <v>-3.854801949901379</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.047409551074465</v>
+        <v>1.175256450900964</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7860313666927176</v>
+        <v>0.7420363712854631</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.0721069899885</v>
+        <v>3.162755477946541</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.599024150797541</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.942014784466926</v>
+        <v>-3.915011247906664</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.021861812697023</v>
+        <v>1.149708712523522</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.725822068687433</v>
+        <v>0.6818270732801786</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.034517392010001</v>
+        <v>3.125165879968042</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.597515768837469</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.865592738035</v>
+        <v>-3.838589201474737</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.050922249309722</v>
+        <v>1.178769149136221</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.725822068687433</v>
+        <v>0.6818270732801786</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.033009010049929</v>
+        <v>3.123657498007971</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.597378636272905</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.821219606396431</v>
+        <v>-3.794216069836168</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.068534369400586</v>
+        <v>1.196381269227085</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.7262002049187471</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.059495756468507</v>
+        <v>3.150144244426548</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.591772430411496</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.843699957255316</v>
+        <v>-3.816696420695053</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.053936023195622</v>
+        <v>1.181782923022121</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7701952003260016</v>
+        <v>0.7262002049187471</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.053889550607097</v>
+        <v>3.144538038565138</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.598154187439301</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.79604422669426</v>
+        <v>-3.769040690133997</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.079380072447849</v>
+        <v>1.207226972274348</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8178509308870573</v>
+        <v>0.7738559354798028</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.088864745971535</v>
+        <v>3.179513233929576</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.603046560814025</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.695526068195505</v>
+        <v>-3.668522531635243</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.124479709222076</v>
+        <v>1.252326609048575</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9183690893858119</v>
+        <v>0.8743740939785574</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.154068014445513</v>
+        <v>3.244716502403554</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.589801233289898</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.679620738763153</v>
+        <v>-3.65261720220289</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.117596513470889</v>
+        <v>1.245443413297388</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8392564286765729</v>
+        <v>0.7952614332693184</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.093355090495842</v>
+        <v>3.184003578453883</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.593898935900526</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.634782337154755</v>
+        <v>-3.607778800594492</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.139629576724877</v>
+        <v>1.267476476551376</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8437998616214424</v>
+        <v>0.7998048662141879</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.100178852873392</v>
+        <v>3.190827340831433</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.598059875531604</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.654280793396763</v>
+        <v>-3.6272772568365</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.135991133859152</v>
+        <v>1.263838033685651</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7957152203415381</v>
+        <v>0.7517202249342836</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.075489007736527</v>
+        <v>3.166137495694568</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.603939478059441</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.610077956310862</v>
+        <v>-3.5830744197506</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.159551871221349</v>
+        <v>1.287398771047848</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8399180574274385</v>
+        <v>0.795923062020184</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.107890312515905</v>
+        <v>3.198538800473946</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.602349478528689</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.617637622147909</v>
+        <v>-3.590634085587647</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.154938005355778</v>
+        <v>1.282784905182277</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.8507264660300033</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.139182355391044</v>
+        <v>3.229830843349085</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.653597243711729</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.459346204608637</v>
+        <v>-3.432342668048375</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.269502337554526</v>
+        <v>1.397349237381025</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8947214614372578</v>
+        <v>0.8507264660300033</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.190430120574083</v>
+        <v>3.281078608532125</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.652037948305982</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.251704200974161</v>
+        <v>-3.224700664413898</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.35099984360257</v>
+        <v>1.478846743429069</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.102363465071734</v>
+        <v>1.05836846966448</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.313456027349022</v>
+        <v>3.404104515307063</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.646986176544252</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.200672108251633</v>
+        <v>-3.17366857169137</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.366360908929851</v>
+        <v>1.49420780875635</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.153395557794262</v>
+        <v>1.109400562387008</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.339023511220809</v>
+        <v>3.42967199917885</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.664173580636957</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.135447927124427</v>
+        <v>-3.108444390564165</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.409637985473438</v>
+        <v>1.537484885299937</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.218619738921468</v>
+        <v>1.174624743514213</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.395345423989838</v>
+        <v>3.485993911947879</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.660134552936237</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.098020907053293</v>
+        <v>-3.071017370493031</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.420569765801172</v>
+        <v>1.548416665627671</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.223871276950649</v>
+        <v>1.179876281543395</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.394457319106627</v>
+        <v>3.485105807064668</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.661391345267477</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.118132563088002</v>
+        <v>-3.091129026527739</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.413781895718529</v>
+        <v>1.541628795545028</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.234898621948069</v>
+        <v>1.190903626540814</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.402330518436319</v>
+        <v>3.49297900639436</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.821949116288688</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.089719299988118</v>
+        <v>-3.062715763427855</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.585704971979694</v>
+        <v>1.713551871806192</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.17592305920164</v>
+        <v>1.131928063794385</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.527502951809672</v>
+        <v>3.618151439767713</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.942062025506505</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.014937038963105</v>
+        <v>-2.987933502402843</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.735730785607516</v>
+        <v>1.863577685434015</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.250705320226652</v>
+        <v>1.206710324819398</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.692485217642497</v>
+        <v>3.783133705600538</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.933770001520364</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.988852954699297</v>
+        <v>-2.961849418139035</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.737872395326898</v>
+        <v>1.865719295153397</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.250705320226652</v>
+        <v>1.206710324819398</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.684193193656356</v>
+        <v>3.774841681614397</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.931963197104144</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.900975041590177</v>
+        <v>-3.009247930603888</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.771216756154326</v>
+        <v>1.844953085751235</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.366630962650004</v>
+        <v>1.309982767267863</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.751941774694146</v>
+        <v>3.834998342667256</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.949517602830935</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.892082580196893</v>
+        <v>-3.000355469210605</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.79232814643843</v>
+        <v>1.86606447603534</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.366630962650004</v>
+        <v>1.309982767267863</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.769496180420937</v>
+        <v>3.852552748394047</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.79442494194536</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.941372650235519</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.060558697166771</v>
+        <v>-3.168831586180483</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.716792747055063</v>
+        <v>1.790529076651972</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.338683126933423</v>
+        <v>1.282034931551282</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.744582526395573</v>
+        <v>3.827639094368683</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.922642347423381</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.614302504537331</v>
+        <v>-2.722575393551043</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.876564921294701</v>
+        <v>1.95030125089161</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.24396445726379</v>
+        <v>1.18731626188165</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.669021021781655</v>
+        <v>3.752077589754765</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.913306369920285</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.591581400854179</v>
+        <v>-2.699854289867891</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.876317385264867</v>
+        <v>1.950053714861776</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.24396445726379</v>
+        <v>1.18731626188165</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.65968504427856</v>
+        <v>3.742741612251669</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.072212495771454</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.720783214148221</v>
+        <v>-2.829056103161933</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.983542785798419</v>
+        <v>2.057279115395328</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.114762643969748</v>
+        <v>1.058114448587608</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.741070082153303</v>
+        <v>3.824126650126413</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.109290318265101</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.746657612622247</v>
+        <v>-2.854930501635959</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.010270848902455</v>
+        <v>2.084007178499364</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.159674252681489</v>
+        <v>1.103026057299349</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.805094869873995</v>
+        <v>3.888151437847104</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.105965674254646</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.739602922407073</v>
+        <v>-2.847875811420785</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.00976808097807</v>
+        <v>2.083504410574979</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.166728942896663</v>
+        <v>1.110080747514522</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.806003039992644</v>
+        <v>3.889059607965754</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.115971827899388</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.712651698080585</v>
+        <v>-2.820924587094297</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.030554724353406</v>
+        <v>2.104291053950315</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.181609288924382</v>
+        <v>1.124961093542242</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.824937401254017</v>
+        <v>3.907993969227127</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.300074960044348</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.848604706136902</v>
+        <v>-2.956877595150614</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.160276653275839</v>
+        <v>2.234012982872748</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.181609288924382</v>
+        <v>1.124961093542242</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.009040533398977</v>
+        <v>4.092097101372087</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.292191654947341</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.871012823941774</v>
+        <v>-2.979285712955486</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.143430101056884</v>
+        <v>2.217166430653793</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.181609288924382</v>
+        <v>1.124961093542242</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.00115722830197</v>
+        <v>4.08421379627508</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.294245654496978</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.899237059519374</v>
+        <v>-3.007509948533086</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.134194406375481</v>
+        <v>2.20793073597239</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.181609288924382</v>
+        <v>1.14293784599355</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.003211227851607</v>
+        <v>4.097053847295502</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.350499372218825</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.908677985407904</v>
+        <v>-3.016950874421616</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.186671753741916</v>
+        <v>2.260408083338826</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.304036406467773</v>
+        <v>1.265364963536942</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.132921216099489</v>
+        <v>4.226763835543385</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.353390466764126</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.960951592743545</v>
+        <v>-3.069224481757257</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.168653405352961</v>
+        <v>2.24238973494987</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.251762799132132</v>
+        <v>1.2130913562013</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.104448146243405</v>
+        <v>4.1982907656873</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.351502279657901</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.037281570344451</v>
+        <v>-3.145554459358163</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.136233227206374</v>
+        <v>2.209969556803283</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.251762799132132</v>
+        <v>1.2130913562013</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.102559959137181</v>
+        <v>4.196402578581075</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.346322509260764</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.239535290668805</v>
+        <v>-3.347808179682517</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.050151968679494</v>
+        <v>2.123888298276404</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.049509078807778</v>
+        <v>1.010837635876947</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.976027956545431</v>
+        <v>4.069870575989325</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.344756519470916</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.40110371619606</v>
+        <v>-3.509376605209772</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.983958608678745</v>
+        <v>2.057694938275654</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.922726155009899</v>
+        <v>0.8840547120790675</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.898392212476856</v>
+        <v>3.992234831920751</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.357829926336835</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.509404378066179</v>
+        <v>-3.617677267079891</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.953711750796615</v>
+        <v>2.027448080393524</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.922726155009899</v>
+        <v>0.8840547120790675</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.911465619342774</v>
+        <v>4.005308238786669</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.349835123119774</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.602551849369546</v>
+        <v>-3.710824738383258</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.908457959058209</v>
+        <v>1.982194288655118</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7998969437273662</v>
+        <v>0.7612255007965347</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.829773289356194</v>
+        <v>3.923615908800089</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.348359164246776</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.630452636479019</v>
+        <v>-3.738725525492731</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.895821685341422</v>
+        <v>1.969558014938331</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7653000195844314</v>
+        <v>0.7266285766535999</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.807539175997436</v>
+        <v>3.90138179544133</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.345123608223975</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.752978739181913</v>
+        <v>-3.861251628195625</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.843575688237463</v>
+        <v>1.917312017834372</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6427739168815375</v>
+        <v>0.604102473950706</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.730787958352898</v>
+        <v>3.824630577796793</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.411829567814479</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.983493235367502</v>
+        <v>-4.091766124381214</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.818075849353731</v>
+        <v>1.89181217895064</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4122594206959488</v>
+        <v>0.3735879777651173</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.659185220232049</v>
+        <v>3.753027839675943</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.552141286816326</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.240214053362326</v>
+        <v>-4.348486942376038</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.855699241157648</v>
+        <v>1.929435570754557</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.303844846552134</v>
+        <v>0.2651734036213025</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.734448194747606</v>
+        <v>3.828290814191502</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.621121555961966</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.394200471138467</v>
+        <v>-4.502473360152178</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.863084943192832</v>
+        <v>1.936821272789741</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.303844846552134</v>
+        <v>0.2651734036213025</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.803428463893246</v>
+        <v>3.897271083337142</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423382</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.607172758082087</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.343678567310801</v>
+        <v>-4.451951456324513</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.869344906844019</v>
+        <v>1.943081236440928</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.303844846552134</v>
+        <v>0.2651734036213025</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.789479666013367</v>
+        <v>3.883322285457262</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609748</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.619043247137501</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.596153721318525</v>
+        <v>-4.704426610332237</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.780225334296343</v>
+        <v>1.853961663893253</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.303844846552134</v>
+        <v>0.2651734036213025</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.801350155068781</v>
+        <v>3.895192774512676</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973152</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.620253781656444</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.889049477797937</v>
+        <v>-4.997322366811649</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.664277566223522</v>
+        <v>1.738013895820431</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.303844846552134</v>
+        <v>0.2651734036213025</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.802560689587725</v>
+        <v>3.89640330903162</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251941</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.624375523883766</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.075713605932745</v>
+        <v>-5.183986494946457</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.59373365719692</v>
+        <v>1.667469986793829</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2771058757275741</v>
+        <v>0.2384344327967426</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.790639049320311</v>
+        <v>3.884481668764205</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.619453376619955</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.221734292846707</v>
+        <v>-5.330007181860419</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.530403235167525</v>
+        <v>1.604139564764434</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2680227839337171</v>
+        <v>0.2293513410028856</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.780267046980186</v>
+        <v>3.874109666424081</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.781657433318999</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.313448301956292</v>
+        <v>-5.421721190970004</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.655921688222735</v>
+        <v>1.729658017819645</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2680227839337171</v>
+        <v>0.2293513410028856</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94247110367923</v>
+        <v>4.036313723123125</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.776504071282814</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.345099961016262</v>
+        <v>-5.453372850029973</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.638107662562561</v>
+        <v>1.711843992159471</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2628543266892769</v>
+        <v>0.2241828837584454</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93421666729638</v>
+        <v>4.028059286740275</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.786733488851305</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.427034779285145</v>
+        <v>-5.535307668298857</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.615563152823499</v>
+        <v>1.689299482420409</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2529195811021967</v>
+        <v>0.2142481381713652</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.938485237512623</v>
+        <v>4.032327856956518</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.795659127307207</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.529010901533552</v>
+        <v>-5.637283790547264</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.583698342380039</v>
+        <v>1.657434671976948</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1509434588537891</v>
+        <v>0.1122720159229577</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.886225202619481</v>
+        <v>3.980067822063376</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231802</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.787812014551383</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.419004618056331</v>
+        <v>-5.527277507070043</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.619853743015103</v>
+        <v>1.693590072612012</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1741480307710643</v>
+        <v>0.1354765878402329</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.892300833014021</v>
+        <v>3.986143452457917</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.792062025273357</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.275945042315405</v>
+        <v>-5.384217931329117</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.681327584033448</v>
+        <v>1.755063913630357</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1821614573610436</v>
+        <v>0.1434900144302121</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.901358899689983</v>
+        <v>3.995201519133878</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.799322908155893</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.974498316843567</v>
+        <v>-5.082771205857279</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.809167157104719</v>
+        <v>1.882903486701628</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4836081828328809</v>
+        <v>0.4449367399020494</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.089487817855622</v>
+        <v>4.183330437299516</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679619</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.800294085908603</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.999088561078751</v>
+        <v>-5.107361450092463</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.800302237163356</v>
+        <v>1.874038566760265</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4836081828328809</v>
+        <v>0.4449367399020494</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.090458995608333</v>
+        <v>4.184301615052227</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.801136990288359</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.948050185072231</v>
+        <v>-5.056323074085943</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.821560491945719</v>
+        <v>1.895296821542628</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4836081828328809</v>
+        <v>0.4449367399020494</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.091301899988088</v>
+        <v>4.185144519431982</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969537</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.820175089162504</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.9069108902056</v>
+        <v>-5.015183779219312</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.857054308766517</v>
+        <v>1.930790638363426</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5247474776995117</v>
+        <v>0.4860760347686802</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.135023575782212</v>
+        <v>4.228866195226106</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.636359085286439</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.81027597818696</v>
+        <v>-4.918548867200672</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.711892269697908</v>
+        <v>1.785628599294816</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6213823897181516</v>
+        <v>0.5827109467873202</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.00918851911733</v>
+        <v>4.103031138561224</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.639861129360403</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.940856712717802</v>
+        <v>-5.049129601731514</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.663162019959535</v>
+        <v>1.736898349556443</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4908016551873091</v>
+        <v>0.4521302122564776</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.934342122472788</v>
+        <v>4.028184741916683</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.624287948436486</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.77636037852684</v>
+        <v>-4.884633267540552</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.713387372712002</v>
+        <v>1.78712370230891</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.655297989378271</v>
+        <v>0.6166265464474395</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.017466742063449</v>
+        <v>4.111309361507343</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077622</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.623475658872915</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.803730311211273</v>
+        <v>-4.912003200224984</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.701627110074659</v>
+        <v>1.775363439671567</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.655297989378271</v>
+        <v>0.6166265464474395</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.016654452499878</v>
+        <v>4.110497071943772</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.633344437997988</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.814115506101162</v>
+        <v>-4.922388395114874</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.707341811243776</v>
+        <v>1.781078140840684</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6449127944883817</v>
+        <v>0.6062413515575502</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.020292114691017</v>
+        <v>4.114134734134911</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.704181443774413</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.832703664823387</v>
+        <v>-4.940976553837099</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.770743553531311</v>
+        <v>1.844479883128219</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6263246357661563</v>
+        <v>0.5876531928353248</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.079976225234107</v>
+        <v>4.173818844678001</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.701050454592711</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.833002211519423</v>
+        <v>-4.941275100533135</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.767493145671195</v>
+        <v>1.841229475268103</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6260260890701204</v>
+        <v>0.5873546461392889</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.076666108034784</v>
+        <v>4.170508727478678</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210885</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.705581349532103</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.732179077828995</v>
+        <v>-4.840451966842707</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.812353294086757</v>
+        <v>1.886089623683666</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6384903045544742</v>
+        <v>0.5998188616236427</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.088675532264787</v>
+        <v>4.182518151708682</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121459</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.705710603010646</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.541397717076588</v>
+        <v>-4.6496706060903</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.888795091866263</v>
+        <v>1.962531421463172</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8292716653068816</v>
+        <v>0.7906002223760501</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.203273602194775</v>
+        <v>4.297116221638669</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906073</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.685547448748243</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.522880863034768</v>
+        <v>-4.63115375204848</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.876038679220588</v>
+        <v>1.949775008817497</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8422017947320898</v>
+        <v>0.8035303518012583</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.190868525587497</v>
+        <v>4.284711145031391</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912978</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.720514385360301</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.467550275133005</v>
+        <v>-4.575823164146717</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.933137850993352</v>
+        <v>2.00687418059026</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8975323826338519</v>
+        <v>0.8588609397030205</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.259033814940612</v>
+        <v>4.352876434384506</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539887</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.714200953261739</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.455496148220043</v>
+        <v>-4.563769037233754</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.931646069659974</v>
+        <v>2.005382399256883</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9095865095468147</v>
+        <v>0.8709150666159833</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.259952858989828</v>
+        <v>4.353795478433722</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811002</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.716081583445875</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.496651267788264</v>
+        <v>-4.604924156801975</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.917064652016822</v>
+        <v>1.99080098161373</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8684313899785938</v>
+        <v>0.8297599470477623</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.237140417433031</v>
+        <v>4.330983036876925</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.728932609323757</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.393770678259671</v>
+        <v>-4.502043567273383</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.971067913706142</v>
+        <v>2.04480424330305</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9713119795071867</v>
+        <v>0.9326405365763553</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.311719797028069</v>
+        <v>4.405562416471963</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.749135279497351</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.625371071429171</v>
+        <v>-4.733643960442883</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.898630426611936</v>
+        <v>1.972366756208844</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9713119795071867</v>
+        <v>0.9326405365763553</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.331922467201664</v>
+        <v>4.425765086645558</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.749135279497351</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.643443579720783</v>
+        <v>-4.751716468734495</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.891401423295291</v>
+        <v>1.965137752892199</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9713119795071867</v>
+        <v>0.9326405365763553</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.331922467201664</v>
+        <v>4.425765086645558</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082828</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.709387193090818</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.874617373597415</v>
+        <v>-4.982890262611127</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.759183819338105</v>
+        <v>1.832920148935013</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9713119795071867</v>
+        <v>0.9326405365763553</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.29217438079513</v>
+        <v>4.386017000239025</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74559333394358</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.716409812087758</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.84333135305696</v>
+        <v>-4.951604242070672</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.778720846551227</v>
+        <v>1.852457176148135</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.002598000047642</v>
+        <v>0.9639265571168106</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.317968612116344</v>
+        <v>4.411811231560238</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677818</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.815580811660662</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.690305960943675</v>
+        <v>-4.798578849957387</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.939102002969445</v>
+        <v>2.012838332566353</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.155623392160926</v>
+        <v>1.116951949230095</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.508954846957218</v>
+        <v>4.602797466401112</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.003047036568955</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.718613274816946</v>
+        <v>-4.826886163830657</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.115245302328429</v>
+        <v>2.188981631925337</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.155623392160926</v>
+        <v>1.116951949230095</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.696421071865511</v>
+        <v>4.790263691309405</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903163</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.972449987923037</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.885206499930468</v>
+        <v>-4.99347938894418</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.018010963637102</v>
+        <v>2.091747293234011</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9890301670474038</v>
+        <v>0.9503587241165723</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.565868088151479</v>
+        <v>4.659710707595373</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568377</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.976126390584755</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.712142120548168</v>
+        <v>-4.82041500956188</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.09091311805174</v>
+        <v>2.164649447648649</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9890301670474038</v>
+        <v>0.9503587241165723</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.569544490813197</v>
+        <v>4.663387110257091</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682199</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.97374444570825</v>
+        <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.682896140092471</v>
+        <v>-4.791169029106183</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.100229565357514</v>
+        <v>2.173965894954422</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9890301670474038</v>
+        <v>0.9503587241165723</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.567162545936692</v>
+        <v>4.661005165380587</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539102</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.971037684865885</v>
+        <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.789821687970322</v>
+        <v>-4.898094576984034</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.054752585364009</v>
+        <v>2.128488914960917</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8821046191695524</v>
+        <v>0.8434331762387209</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.500300456367617</v>
+        <v>4.594143075811511</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983732</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.972466487009119</v>
+        <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.934840246477571</v>
+        <v>-5.043113135491283</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.998173964104343</v>
+        <v>2.071910293701252</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7370860606623039</v>
+        <v>0.6984146177314724</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.414718123406502</v>
+        <v>4.508560742850396</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969743</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.072397726266872</v>
+        <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.053182012262289</v>
+        <v>-5.161454901276</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.050768497048209</v>
+        <v>2.124504826645118</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7477720992251939</v>
+        <v>0.7091006562943625</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.521060985801989</v>
+        <v>4.614903605245883</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073533</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.070183423392811</v>
+        <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.104592434582996</v>
+        <v>-5.212865323596708</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.027990025245865</v>
+        <v>2.101726354842773</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7477720992251939</v>
+        <v>0.7091006562943625</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.518846682927927</v>
+        <v>4.612689302371821</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70477813472006</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.0700865514671</v>
+        <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.184011885790748</v>
+        <v>-5.29228477480446</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.996125372837054</v>
+        <v>2.069861702433962</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7477720992251939</v>
+        <v>0.7091006562943625</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.518749811002217</v>
+        <v>4.612592430446111</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.070080445025144</v>
+        <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.279474883707966</v>
+        <v>-5.387747772721678</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.95793406722821</v>
+        <v>2.031670396825118</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7477720992251939</v>
+        <v>0.7091006562943625</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.518743704560261</v>
+        <v>4.612586324004154</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.068176841587754</v>
+        <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.31949488175175</v>
+        <v>-5.427767770765461</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.940022464573307</v>
+        <v>2.013758794170216</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7077521011814101</v>
+        <v>0.6690806582505786</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.492828102296601</v>
+        <v>4.586670721740495</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636265</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.073910659335481</v>
+        <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.374864043883943</v>
+        <v>-5.483136932897655</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.923608617468156</v>
+        <v>1.997344947065065</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7077521011814101</v>
+        <v>0.6690806582505786</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.498561920044327</v>
+        <v>4.592404539488221</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396008</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.073449022678414</v>
+        <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.42030182371477</v>
+        <v>-5.528574712728482</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.904971868878758</v>
+        <v>1.978708198475667</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6649071105032505</v>
+        <v>0.626235667572419</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.472393288980364</v>
+        <v>4.566235908424258</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396417</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.093323415528733</v>
+        <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.337076366867106</v>
+        <v>-5.445349255880818</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.958136444468143</v>
+        <v>2.031872774065052</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6649071105032505</v>
+        <v>0.626235667572419</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.492267681830683</v>
+        <v>4.586110301274577</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.742792842057662</v>
+        <v>3.794507029299178</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.077024116053461</v>
+        <v>4.194069601255854</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.160786142261799</v>
+        <v>-5.269059031275511</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.012353234834994</v>
+        <v>2.086089564431902</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6649071105032505</v>
+        <v>0.626235667572419</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.475968382355411</v>
+        <v>4.569811001799305</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.592178508075042</v>
+        <v>3.775770819058497</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.225596458839967</v>
+        <v>4.588800934539057</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.018408802494468</v>
+        <v>-5.154447306635298</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.217876513528433</v>
+        <v>2.52666558757119</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6649071105032505</v>
+        <v>0.7296923356655732</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.624540725141918</v>
+        <v>5.026616335938401</v>
       </c>
     </row>
   </sheetData>
